--- a/static/excel/META_model.xlsx
+++ b/static/excel/META_model.xlsx
@@ -7344,11 +7344,11 @@
         </is>
       </c>
       <c r="B5" s="43" t="n">
-        <v>1569837.146156</v>
+        <v>1559175.768128</v>
       </c>
       <c r="C5" s="44" t="inlineStr">
         <is>
-          <t>FMP marketCap  |  price $618.43</t>
+          <t>FMP marketCap  |  price $614.23</t>
         </is>
       </c>
     </row>
@@ -7430,11 +7430,11 @@
         </is>
       </c>
       <c r="B12" s="46" t="n">
-        <v>0.0446</v>
+        <v>0.0447</v>
       </c>
       <c r="C12" s="44" t="inlineStr">
         <is>
-          <t>FRED series DGS10  |  latest: 2026-05-13</t>
+          <t>FRED series DGS10  |  latest: 2026-05-14</t>
         </is>
       </c>
     </row>
@@ -7445,7 +7445,7 @@
         </is>
       </c>
       <c r="B13" s="48" t="n">
-        <v>0.0446</v>
+        <v>0.0447</v>
       </c>
       <c r="C13" s="49" t="inlineStr">
         <is>
@@ -7517,7 +7517,7 @@
         </is>
       </c>
       <c r="B19" s="50" t="n">
-        <v>1.149</v>
+        <v>1.15</v>
       </c>
       <c r="C19" s="44">
         <f> unlevered × (1 + (1 − t) × D/E)</f>
@@ -7703,11 +7703,11 @@
         </is>
       </c>
       <c r="B35" s="46" t="n">
-        <v>0.05</v>
+        <v>0.0501</v>
       </c>
       <c r="C35" s="44" t="inlineStr">
         <is>
-          <t>Rf 4.46% + spread 0.54%</t>
+          <t>Rf 4.47% + spread 0.54%</t>
         </is>
       </c>
     </row>
@@ -9965,7 +9965,7 @@
         </is>
       </c>
       <c r="B61" s="111" t="n">
-        <v>618.4299999999999</v>
+        <v>614.23</v>
       </c>
       <c r="C61" s="103" t="n"/>
       <c r="D61" s="103" t="n"/>
@@ -10065,7 +10065,7 @@
     <row r="1" ht="18" customHeight="1">
       <c r="A1" s="113" t="inlineStr">
         <is>
-          <t>JS SCORECARD — META  |  Master Prompt v2  |  15 May 2026  |  Sector bucket: Tech Growth</t>
+          <t>JS SCORECARD — META  |  Master Prompt v2  |  16 May 2026  |  Sector bucket: Tech Growth</t>
         </is>
       </c>
     </row>
@@ -10265,7 +10265,7 @@
       </c>
       <c r="D11" s="129" t="inlineStr">
         <is>
-          <t>ROIC trend +5.1% ✓ (≥-2pp)  |  GM maintained +3.7% ✓  |  Op margin +16.6% ✓ (≥-2pp)  |  Capital returns MOD-LOW ✗  |  Share count -2.7%/yr ✓ (net buyback)  |  Goodwill/Equity 11% ✓ (&lt;40%)  [5/6 indicators positive — proxy score]</t>
+          <t>ROIC trend +5.1% ✓ (&gt;=-2pp)  |  GM maintained +3.7% ✓  |  Op margin +16.6% ✓ (≥-2pp)  |  Capital returns MOD-LOW ✗  |  Share count -2.7%/yr ✓ (net buyback)  |  Goodwill/Equity 11% ✓ (&lt;40%)  [5/6 indicators positive — proxy score]</t>
         </is>
       </c>
       <c r="E11" s="130" t="inlineStr">
@@ -10282,7 +10282,7 @@
       </c>
       <c r="H11" s="133" t="inlineStr">
         <is>
-          <t>ROIC trend +5.1% ✓ (≥-2pp)  |  GM maintained +3.7% ✓  |  Op margin +16.6% ✓ (≥-2pp)  |  Capital returns MOD-LOW ✗  |  Share count -2.7%/yr ✓ (net buyback)  |  Goodwill/Equity 11% ✓ (&lt;40%)  [5/6 indicators positive — proxy score]</t>
+          <t>ROIC trend +5.1% ✓ (&gt;=-2pp)  |  GM maintained +3.7% ✓  |  Op margin +16.6% ✓ (≥-2pp)  |  Capital returns MOD-LOW ✗  |  Share count -2.7%/yr ✓ (net buyback)  |  Goodwill/Equity 11% ✓ (&lt;40%)  [5/6 indicators positive — proxy score]</t>
         </is>
       </c>
     </row>

--- a/static/excel/META_model.xlsx
+++ b/static/excel/META_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Cover" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="P&amp;L" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Balance Sheet" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Cash Flow" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Ratios &amp; FCF" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Segments" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="WACC" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="DCF" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Scorecard" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="P&amp;L" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance Sheet" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flow" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ratios &amp; FCF" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Segments" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WACC" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DCF" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scorecard" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -7344,11 +7344,11 @@
         </is>
       </c>
       <c r="B5" s="43" t="n">
-        <v>1559175.768128</v>
+        <v>1549098.286664</v>
       </c>
       <c r="C5" s="44" t="inlineStr">
         <is>
-          <t>FMP marketCap  |  price $614.23</t>
+          <t>FMP marketCap  |  price $610.26</t>
         </is>
       </c>
     </row>
@@ -7430,11 +7430,11 @@
         </is>
       </c>
       <c r="B12" s="46" t="n">
-        <v>0.0447</v>
+        <v>0.0457</v>
       </c>
       <c r="C12" s="44" t="inlineStr">
         <is>
-          <t>FRED series DGS10  |  latest: 2026-05-14</t>
+          <t>FRED series DGS10  |  latest: 2026-05-21</t>
         </is>
       </c>
     </row>
@@ -7445,7 +7445,7 @@
         </is>
       </c>
       <c r="B13" s="48" t="n">
-        <v>0.0447</v>
+        <v>0.0457</v>
       </c>
       <c r="C13" s="49" t="inlineStr">
         <is>
@@ -7703,11 +7703,11 @@
         </is>
       </c>
       <c r="B35" s="46" t="n">
-        <v>0.0501</v>
+        <v>0.05110000000000001</v>
       </c>
       <c r="C35" s="44" t="inlineStr">
         <is>
-          <t>Rf 4.47% + spread 0.54%</t>
+          <t>Rf 4.57% + spread 0.54%</t>
         </is>
       </c>
     </row>
@@ -7746,7 +7746,7 @@
         </is>
       </c>
       <c r="B38" s="48" t="n">
-        <v>0.025</v>
+        <v>0.0256</v>
       </c>
       <c r="C38" s="49" t="inlineStr">
         <is>
@@ -7811,16 +7811,16 @@
     <row r="45" ht="22" customHeight="1">
       <c r="A45" s="54" t="inlineStr">
         <is>
-          <t>WACC  =  (E/V × Re)  +  (D/V × Rd × (1 − t))</t>
+          <t>WACC  =  MAX(8.5%, (E/V × Re) + (D/V × Rd × (1 − t)))</t>
         </is>
       </c>
       <c r="B45" s="55">
-        <f>B8*B28+B9*B38*(1-B42)</f>
+        <f>MAX(0.085, B8*B28+B9*B38*(1-B42))</f>
         <v/>
       </c>
       <c r="C45" s="56" t="inlineStr">
         <is>
-          <t>Used as discount rate in DCF tab</t>
+          <t>Floored 8.5% (D-001); raw formula below</t>
         </is>
       </c>
     </row>
@@ -8183,13 +8183,13 @@
         <v/>
       </c>
       <c r="G7" s="71" t="n">
-        <v>0.2579</v>
+        <v>0.2581</v>
       </c>
       <c r="H7" s="71" t="n">
-        <v>0.1907</v>
+        <v>0.1917</v>
       </c>
       <c r="I7" s="71" t="n">
-        <v>0.1669</v>
+        <v>0.1659</v>
       </c>
       <c r="J7" s="72">
         <f>I7</f>
@@ -8533,13 +8533,13 @@
         <v/>
       </c>
       <c r="G15" s="77" t="n">
-        <v>252803.5</v>
+        <v>252844</v>
       </c>
       <c r="H15" s="77" t="n">
-        <v>301024.4</v>
+        <v>301316.3</v>
       </c>
       <c r="I15" s="77" t="n">
-        <v>351265.2</v>
+        <v>351301.6</v>
       </c>
       <c r="J15" s="78">
         <f>I15*(1+J7)</f>
@@ -8567,27 +8567,27 @@
       </c>
       <c r="G16" s="82" t="inlineStr">
         <is>
-          <t>249,218 — 257,897</t>
+          <t>249,120 — 257,795</t>
         </is>
       </c>
       <c r="H16" s="82" t="inlineStr">
         <is>
-          <t>292,004 — 317,257</t>
+          <t>292,017 — 317,272</t>
         </is>
       </c>
       <c r="I16" s="82" t="inlineStr">
         <is>
-          <t>350,559 — 351,972</t>
+          <t>350,615 — 351,988</t>
         </is>
       </c>
       <c r="J16" s="82" t="inlineStr">
         <is>
-          <t>390,781 — 423,617</t>
+          <t>390,555 — 423,372</t>
         </is>
       </c>
       <c r="K16" s="82" t="inlineStr">
         <is>
-          <t>448,044 — 485,692</t>
+          <t>447,786 — 485,412</t>
         </is>
       </c>
       <c r="L16" s="83" t="inlineStr">
@@ -8608,7 +8608,7 @@
         </is>
       </c>
       <c r="G17" s="84" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H17" s="84" t="n">
         <v>44</v>
@@ -8731,13 +8731,13 @@
         <v/>
       </c>
       <c r="G20" s="77" t="n">
-        <v>115177.7</v>
+        <v>115196.2</v>
       </c>
       <c r="H20" s="77" t="n">
-        <v>137147.2</v>
+        <v>137280.2</v>
       </c>
       <c r="I20" s="77" t="n">
-        <v>160037</v>
+        <v>160053.6</v>
       </c>
       <c r="J20" s="78">
         <f>J15*J8</f>
@@ -8765,27 +8765,27 @@
       </c>
       <c r="G21" s="82" t="inlineStr">
         <is>
-          <t>113,544 — 117,498</t>
+          <t>113,500 — 117,452</t>
         </is>
       </c>
       <c r="H21" s="82" t="inlineStr">
         <is>
-          <t>133,037 — 144,543</t>
+          <t>133,044 — 144,550</t>
         </is>
       </c>
       <c r="I21" s="82" t="inlineStr">
         <is>
-          <t>159,715 — 160,359</t>
+          <t>159,741 — 160,366</t>
         </is>
       </c>
       <c r="J21" s="82" t="inlineStr">
         <is>
-          <t>178,040 — 193,000</t>
+          <t>177,938 — 192,889</t>
         </is>
       </c>
       <c r="K21" s="82" t="inlineStr">
         <is>
-          <t>204,130 — 221,282</t>
+          <t>204,012 — 221,154</t>
         </is>
       </c>
       <c r="L21" s="83" t="inlineStr">
@@ -9965,7 +9965,7 @@
         </is>
       </c>
       <c r="B61" s="111" t="n">
-        <v>614.23</v>
+        <v>610.26</v>
       </c>
       <c r="C61" s="103" t="n"/>
       <c r="D61" s="103" t="n"/>
@@ -10065,7 +10065,7 @@
     <row r="1" ht="18" customHeight="1">
       <c r="A1" s="113" t="inlineStr">
         <is>
-          <t>JS SCORECARD — META  |  Master Prompt v2  |  16 May 2026  |  Sector bucket: Tech Growth</t>
+          <t>JS SCORECARD — META  |  Master Prompt v2  |  25 May 2026  |  Sector bucket: Tech Growth</t>
         </is>
       </c>
     </row>
@@ -10198,7 +10198,7 @@
       </c>
       <c r="D9" s="129" t="inlineStr">
         <is>
-          <t>GM 82.0% ✓ (&gt;40%)  |  GM trend +3.7% ✓ (&gt;+1pp)  |  ROIC-WACC +24.4% ✓ (&gt;+5pp)  |  Rev consistency σ=9.5% ✗ (&lt;8%)  [3/4 indicators positive — proxy score]</t>
+          <t>GM 82.0% ✓ (&gt;40%)  |  GM trend +3.7% ✓ (&gt;+1pp)  |  ROIC-WACC +14.9% ✓ (&gt;+5pp)  |  Rev consistency σ=9.5% ✗ (&lt;8%)  [3/4 indicators positive — proxy score]</t>
         </is>
       </c>
       <c r="E9" s="130" t="inlineStr">
@@ -10215,7 +10215,7 @@
       </c>
       <c r="H9" s="133" t="inlineStr">
         <is>
-          <t>GM 82.0% ✓ (&gt;40%)  |  GM trend +3.7% ✓ (&gt;+1pp)  |  ROIC-WACC +24.4% ✓ (&gt;+5pp)  |  Rev consistency σ=9.5% ✗ (&lt;8%)  [3/4 indicators positive — proxy score]</t>
+          <t>GM 82.0% ✓ (&gt;40%)  |  GM trend +3.7% ✓ (&gt;+1pp)  |  ROIC-WACC +14.9% ✓ (&gt;+5pp)  |  Rev consistency σ=9.5% ✗ (&lt;8%)  [3/4 indicators positive — proxy score]</t>
         </is>
       </c>
     </row>
@@ -10318,7 +10318,7 @@
         </is>
       </c>
       <c r="F13" s="131" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G13" s="132">
         <f>IF(F13="",0,C13*F13*10)</f>
@@ -10429,7 +10429,7 @@
         </is>
       </c>
       <c r="F16" s="131" t="n">
-        <v>10.3</v>
+        <v>10</v>
       </c>
       <c r="G16" s="132">
         <f>IF(F16="",0,C16*F16*10)</f>
@@ -10473,7 +10473,7 @@
         </is>
       </c>
       <c r="F18" s="131" t="n">
-        <v>11.54</v>
+        <v>10</v>
       </c>
       <c r="G18" s="132">
         <f>IF(F18="",0,C18*F18*10)</f>
@@ -10510,7 +10510,7 @@
         </is>
       </c>
       <c r="F19" s="131" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G19" s="132">
         <f>IF(F19="",0,C19*F19*10)</f>
@@ -10538,7 +10538,7 @@
       </c>
       <c r="D20" s="129" t="inlineStr">
         <is>
-          <t>Rev growth σ=9.5%  |  Op margin σ=6.4%  [proxy — lower σ = lower risk = higher score]</t>
+          <t>Rev growth σ=9.5%  |  OM trend +1.8%, σ=6.4%  [quality = direction + stability]</t>
         </is>
       </c>
       <c r="E20" s="135" t="inlineStr">
@@ -10547,7 +10547,7 @@
         </is>
       </c>
       <c r="F20" s="131" t="n">
-        <v>5</v>
+        <v>3.33</v>
       </c>
       <c r="G20" s="132">
         <f>IF(F20="",0,C20*F20*10)</f>
@@ -10555,7 +10555,7 @@
       </c>
       <c r="H20" s="133" t="inlineStr">
         <is>
-          <t>Rev growth σ=9.5%  |  Op margin σ=6.4%  [proxy — lower σ = lower risk = higher score]</t>
+          <t>Rev growth σ=9.5%  |  OM trend +1.8%, σ=6.4%  [quality = direction + stability]</t>
         </is>
       </c>
     </row>
@@ -10582,16 +10582,16 @@
       </c>
       <c r="D22" s="129" t="inlineStr">
         <is>
-          <t>Current 27.5x  |  5yr avg 22.5x  |  DCF-implied 20.9x  [+32% vs benchmark]</t>
-        </is>
-      </c>
-      <c r="E22" s="136" t="inlineStr">
-        <is>
-          <t>LOW</t>
+          <t>Current 27.5x  |  5yr avg 22.5x  |  DCF-implied 20.5x [ref only — not used as benchmark]  [+22% vs benchmark]  [trail=3.44 | fwd_pe=18.6x→9.60 | abs=4.0 → blended 40/40/20=6.02]  PEG=50.39 (fwd_pe=18.6x / eps_growth=37%)  [revision:Strong upgrade cycle→+0.50]</t>
+        </is>
+      </c>
+      <c r="E22" s="135" t="inlineStr">
+        <is>
+          <t>MOD-LOW</t>
         </is>
       </c>
       <c r="F22" s="131" t="n">
-        <v>2.21</v>
+        <v>6.52</v>
       </c>
       <c r="G22" s="132">
         <f>IF(F22="",0,C22*F22*10)</f>
@@ -10599,7 +10599,7 @@
       </c>
       <c r="H22" s="133" t="inlineStr">
         <is>
-          <t>Current 27.5x  |  5yr avg 22.5x  |  DCF-implied 20.9x  [+32% vs benchmark]</t>
+          <t>Current 27.5x  |  5yr avg 22.5x  |  DCF-implied 20.5x [ref only — not used as benchmark]  [+22% vs benchmark]  [trail=3.44 | fwd_pe=18.6x→9.60 | abs=4.0 → blended 40/40/20=6.02]  PEG=50.39 (fwd_pe=18.6x / eps_growth=37%)  [revision:Strong upgrade cycle→+0.50]</t>
         </is>
       </c>
     </row>
@@ -10619,7 +10619,7 @@
       </c>
       <c r="D23" s="129" t="inlineStr">
         <is>
-          <t>Current 36.1x  |  5yr avg 25.1x  |  DCF-implied 27.5x  [+44% vs benchmark]</t>
+          <t>Current 36.1x  |  5yr avg 25.1x  |  DCF-implied 26.9x [ref only — not used as benchmark]  [+44% vs benchmark]  [trail=0.74 | fwd_pfcf=26.5x→6.11 | abs=4.0 → blended 40/40/20=3.54]  [fcf_yield=2.8% vs rf=4.6%  spread=-1.8%→modifier=-0.25]</t>
         </is>
       </c>
       <c r="E23" s="136" t="inlineStr">
@@ -10628,7 +10628,7 @@
         </is>
       </c>
       <c r="F23" s="131" t="n">
-        <v>0.74</v>
+        <v>3.29</v>
       </c>
       <c r="G23" s="132">
         <f>IF(F23="",0,C23*F23*10)</f>
@@ -10636,7 +10636,7 @@
       </c>
       <c r="H23" s="133" t="inlineStr">
         <is>
-          <t>Current 36.1x  |  5yr avg 25.1x  |  DCF-implied 27.5x  [+44% vs benchmark]</t>
+          <t>Current 36.1x  |  5yr avg 25.1x  |  DCF-implied 26.9x [ref only — not used as benchmark]  [+44% vs benchmark]  [trail=0.74 | fwd_pfcf=26.5x→6.11 | abs=4.0 → blended 40/40/20=3.54]  [fcf_yield=2.8% vs rf=4.6%  spread=-1.8%→modifier=-0.25]</t>
         </is>
       </c>
     </row>

--- a/static/excel/META_model.xlsx
+++ b/static/excel/META_model.xlsx
@@ -7430,11 +7430,11 @@
         </is>
       </c>
       <c r="B12" s="46" t="n">
-        <v>0.0457</v>
+        <v>0.04559999999999999</v>
       </c>
       <c r="C12" s="44" t="inlineStr">
         <is>
-          <t>FRED series DGS10  |  latest: 2026-05-21</t>
+          <t>FRED series DGS10  |  latest: 2026-05-22</t>
         </is>
       </c>
     </row>
@@ -7445,7 +7445,7 @@
         </is>
       </c>
       <c r="B13" s="48" t="n">
-        <v>0.0457</v>
+        <v>0.0456</v>
       </c>
       <c r="C13" s="49" t="inlineStr">
         <is>
@@ -7644,25 +7644,27 @@
       </c>
       <c r="B31" s="53" t="inlineStr">
         <is>
-          <t>Not available</t>
+          <t>AA-</t>
         </is>
       </c>
       <c r="C31" s="44" t="inlineStr">
         <is>
-          <t>FMP /ratings endpoint</t>
+          <t>User input</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="17" t="inlineStr">
         <is>
-          <t>FRED matched yield</t>
-        </is>
-      </c>
-      <c r="B32" s="53" t="n"/>
+          <t>FRED matched yield  (rating-tier index)</t>
+        </is>
+      </c>
+      <c r="B32" s="46" t="n">
+        <v>0.0496</v>
+      </c>
       <c r="C32" s="44" t="inlineStr">
         <is>
-          <t>No rating returned — FRED method not applicable</t>
+          <t>FRED BAMLC0A2CAAEY — AA</t>
         </is>
       </c>
     </row>
@@ -7703,11 +7705,11 @@
         </is>
       </c>
       <c r="B35" s="46" t="n">
-        <v>0.05110000000000001</v>
+        <v>0.051</v>
       </c>
       <c r="C35" s="44" t="inlineStr">
         <is>
-          <t>Rf 4.57% + spread 0.54%</t>
+          <t>Rf 4.56% + spread 0.54%</t>
         </is>
       </c>
     </row>
@@ -7746,11 +7748,11 @@
         </is>
       </c>
       <c r="B38" s="48" t="n">
-        <v>0.0256</v>
+        <v>0.0335</v>
       </c>
       <c r="C38" s="49" t="inlineStr">
         <is>
-          <t>Default = average of 2 source(s) above — override freely</t>
+          <t>Default = average of 3 source(s) above — override freely</t>
         </is>
       </c>
     </row>
@@ -10065,7 +10067,7 @@
     <row r="1" ht="18" customHeight="1">
       <c r="A1" s="113" t="inlineStr">
         <is>
-          <t>JS SCORECARD — META  |  Master Prompt v2  |  25 May 2026  |  Sector bucket: Tech Growth</t>
+          <t>JS SCORECARD — META  |  Master Prompt v2  |  27 May 2026  |  Sector bucket: Tech Growth</t>
         </is>
       </c>
     </row>
@@ -10582,16 +10584,16 @@
       </c>
       <c r="D22" s="129" t="inlineStr">
         <is>
-          <t>Current 27.5x  |  5yr avg 22.5x  |  DCF-implied 20.5x [ref only — not used as benchmark]  [+22% vs benchmark]  [trail=3.44 | fwd_pe=18.6x→9.60 | abs=4.0 → blended 40/40/20=6.02]  PEG=50.39 (fwd_pe=18.6x / eps_growth=37%)  [revision:Strong upgrade cycle→+0.50]</t>
-        </is>
-      </c>
-      <c r="E22" s="135" t="inlineStr">
-        <is>
-          <t>MOD-LOW</t>
+          <t>Fwd P/E 18.6x (scoring basis)  |  5yr avg 23.5x  |  DCF-implied 20.5x [ref only — not used as benchmark]  [-21% vs benchmark]  [trail=10.00 | fwd_pe=18.6x→10.00 | abs=10.0 → blended 40/40/20=10.00]  PEG=50.39 (fwd_pe=18.6x / eps_growth=37%)  [revision:Strong upgrade cycle→+0.50]</t>
+        </is>
+      </c>
+      <c r="E22" s="134" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="F22" s="131" t="n">
-        <v>6.52</v>
+        <v>10.5</v>
       </c>
       <c r="G22" s="132">
         <f>IF(F22="",0,C22*F22*10)</f>
@@ -10599,7 +10601,7 @@
       </c>
       <c r="H22" s="133" t="inlineStr">
         <is>
-          <t>Current 27.5x  |  5yr avg 22.5x  |  DCF-implied 20.5x [ref only — not used as benchmark]  [+22% vs benchmark]  [trail=3.44 | fwd_pe=18.6x→9.60 | abs=4.0 → blended 40/40/20=6.02]  PEG=50.39 (fwd_pe=18.6x / eps_growth=37%)  [revision:Strong upgrade cycle→+0.50]</t>
+          <t>Fwd P/E 18.6x (scoring basis)  |  5yr avg 23.5x  |  DCF-implied 20.5x [ref only — not used as benchmark]  [-21% vs benchmark]  [trail=10.00 | fwd_pe=18.6x→10.00 | abs=10.0 → blended 40/40/20=10.00]  PEG=50.39 (fwd_pe=18.6x / eps_growth=37%)  [revision:Strong upgrade cycle→+0.50]</t>
         </is>
       </c>
     </row>
@@ -10619,7 +10621,7 @@
       </c>
       <c r="D23" s="129" t="inlineStr">
         <is>
-          <t>Current 36.1x  |  5yr avg 25.1x  |  DCF-implied 26.9x [ref only — not used as benchmark]  [+44% vs benchmark]  [trail=0.74 | fwd_pfcf=26.5x→6.11 | abs=4.0 → blended 40/40/20=3.54]  [fcf_yield=2.8% vs rf=4.6%  spread=-1.8%→modifier=-0.25]</t>
+          <t>Current 36.1x  |  5yr avg 27.3x  |  DCF-implied 26.8x [ref only — not used as benchmark]  [+32% vs benchmark]  [trail=2.13 | fwd_pfcf=26.5x→7.44 | abs=4.0 → blended 40/40/20=4.63]  [fcf_yield=2.8% vs rf=4.6%  spread=-1.8%→modifier=-0.25]</t>
         </is>
       </c>
       <c r="E23" s="136" t="inlineStr">
@@ -10628,7 +10630,7 @@
         </is>
       </c>
       <c r="F23" s="131" t="n">
-        <v>3.29</v>
+        <v>4.38</v>
       </c>
       <c r="G23" s="132">
         <f>IF(F23="",0,C23*F23*10)</f>
@@ -10636,7 +10638,7 @@
       </c>
       <c r="H23" s="133" t="inlineStr">
         <is>
-          <t>Current 36.1x  |  5yr avg 25.1x  |  DCF-implied 26.9x [ref only — not used as benchmark]  [+44% vs benchmark]  [trail=0.74 | fwd_pfcf=26.5x→6.11 | abs=4.0 → blended 40/40/20=3.54]  [fcf_yield=2.8% vs rf=4.6%  spread=-1.8%→modifier=-0.25]</t>
+          <t>Current 36.1x  |  5yr avg 27.3x  |  DCF-implied 26.8x [ref only — not used as benchmark]  [+32% vs benchmark]  [trail=2.13 | fwd_pfcf=26.5x→7.44 | abs=4.0 → blended 40/40/20=4.63]  [fcf_yield=2.8% vs rf=4.6%  spread=-1.8%→modifier=-0.25]</t>
         </is>
       </c>
     </row>
